--- a/01_Input/00_CO Validation/Serbia - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Serbia - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27016"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="202" documentId="11_8048FE8377A146D934E2F53C766C1D44588AAA59" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5236E3F9-417B-43F2-BA19-C37E7C89BC88}"/>
+  <xr:revisionPtr revIDLastSave="213" documentId="11_8048FE8377A146D934E2F53C766C1D44588AAA59" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5865B420-1816-4A33-9BD6-31B5904E34C0}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="101">
   <si>
     <t>Project ID</t>
   </si>
@@ -102,7 +102,7 @@
     <t>http://open.undp.org/projects/00122808</t>
   </si>
   <si>
-    <t>Other Energy Services</t>
+    <t>Policy or Regulatory Framework</t>
   </si>
   <si>
     <t>PIU capacitated and operational until the end of the project (Yes/No)</t>
@@ -127,9 +127,6 @@
     <t>Number of detailed Energy Audits (DEA) for selected CGBs conducted</t>
   </si>
   <si>
-    <t>Capacity Training</t>
-  </si>
-  <si>
     <t>Number of workshops for the EECGB Programme beneficiaries, other stakeholders and media organized</t>
   </si>
   <si>
@@ -140,6 +137,9 @@
   </si>
   <si>
     <t>PIMS+</t>
+  </si>
+  <si>
+    <t>Other Energy Services</t>
   </si>
   <si>
     <t>Number of direct project beneficiaries disaggregated by gender (individual people)</t>
@@ -167,6 +167,9 @@
     <t>Beneficiary: users of public buildings (6500)</t>
   </si>
   <si>
+    <t>Energy Saved</t>
+  </si>
+  <si>
     <t>Energy saved (MJ)</t>
   </si>
   <si>
@@ -177,9 +180,6 @@
   </si>
   <si>
     <t>Increase in installed renewable energy capacity (MW)</t>
-  </si>
-  <si>
-    <t>Policy or Regulatory Framework</t>
   </si>
   <si>
     <t>Status of the rulebooks listed under output 1.1 in chapter IV of the Prodoc</t>
@@ -208,6 +208,9 @@
   </si>
   <si>
     <t>Comments</t>
+  </si>
+  <si>
+    <t>Capacity Training</t>
   </si>
   <si>
     <t xml:space="preserve"> 2 340 TJ</t>
@@ -584,6 +587,42 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -598,42 +637,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -955,636 +958,627 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="45.75">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="40" t="s">
+      <c r="F1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="40" t="s">
+      <c r="I1" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="37" t="s">
+      <c r="J1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="37" t="s">
+      <c r="L1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="37" t="s">
+      <c r="M1" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="37" t="s">
+      <c r="N1" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="37" t="s">
+      <c r="O1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="37" t="s">
+      <c r="P1" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="37" t="s">
+      <c r="Q1" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="37" t="s">
+      <c r="R1" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="37" t="s">
+      <c r="S1" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="37" t="s">
+      <c r="T1" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="37" t="s">
+      <c r="U1" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="37" t="s">
+      <c r="V1" s="32" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="60.75">
-      <c r="A2" s="38">
+      <c r="A2" s="33">
         <v>122808</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="42">
+      <c r="D2" s="37">
         <v>1055099</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="E2" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="44" t="s">
+      <c r="F2" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="45">
+      <c r="G2" s="40">
         <v>0</v>
       </c>
-      <c r="H2" s="45"/>
-      <c r="I2" s="44" t="s">
+      <c r="H2" s="40"/>
+      <c r="I2" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="39" t="s">
+      <c r="J2" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="38"/>
-      <c r="L2" s="39" t="s">
+      <c r="K2" s="33"/>
+      <c r="L2" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="46" t="s">
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
+      <c r="T2" s="33"/>
+      <c r="U2" s="33"/>
+      <c r="V2" s="33"/>
     </row>
     <row r="3" spans="1:22" ht="45.75">
-      <c r="A3" s="38"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="43" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="44" t="s">
+      <c r="F3" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="45">
+      <c r="G3" s="40">
         <v>3</v>
       </c>
-      <c r="H3" s="45">
+      <c r="H3" s="40">
         <v>20</v>
       </c>
-      <c r="I3" s="44" t="s">
+      <c r="I3" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="39" t="s">
+      <c r="J3" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="38"/>
-      <c r="L3" s="39" t="s">
+      <c r="K3" s="33"/>
+      <c r="L3" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
-      <c r="U3" s="38"/>
-      <c r="V3" s="38"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="33"/>
+      <c r="O3" s="33"/>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="33"/>
+      <c r="R3" s="33"/>
+      <c r="S3" s="33"/>
+      <c r="T3" s="33"/>
+      <c r="U3" s="33"/>
+      <c r="V3" s="33"/>
     </row>
     <row r="4" spans="1:22" ht="45.75">
-      <c r="A4" s="38"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="43" t="s">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="44" t="s">
+      <c r="F4" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="45">
+      <c r="G4" s="40">
         <v>0</v>
       </c>
-      <c r="H4" s="45">
+      <c r="H4" s="40">
         <v>25</v>
       </c>
-      <c r="I4" s="44" t="s">
+      <c r="I4" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="39" t="s">
+      <c r="J4" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="38"/>
-      <c r="L4" s="39" t="s">
+      <c r="K4" s="33"/>
+      <c r="L4" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="33"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="33"/>
+      <c r="V4" s="33"/>
     </row>
     <row r="5" spans="1:22" ht="91.5" customHeight="1">
-      <c r="A5" s="38"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="43" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="44" t="s">
+      <c r="G5" s="40">
+        <v>0</v>
+      </c>
+      <c r="H5" s="40">
+        <v>1</v>
+      </c>
+      <c r="I5" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="33"/>
+      <c r="L5" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="33"/>
+      <c r="R5" s="33"/>
+      <c r="S5" s="33"/>
+      <c r="T5" s="33"/>
+      <c r="U5" s="33"/>
+      <c r="V5" s="33"/>
+    </row>
+    <row r="6" spans="1:22" ht="121.5" customHeight="1">
+      <c r="A6" s="33"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="45">
+      <c r="G6" s="40">
         <v>0</v>
       </c>
-      <c r="H5" s="45">
+      <c r="H6" s="40">
+        <v>12</v>
+      </c>
+      <c r="I6" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" s="33"/>
+      <c r="L6" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" s="33"/>
+      <c r="N6" s="33"/>
+      <c r="O6" s="33"/>
+      <c r="P6" s="33"/>
+      <c r="Q6" s="33"/>
+      <c r="R6" s="33"/>
+      <c r="S6" s="33"/>
+      <c r="T6" s="33"/>
+      <c r="U6" s="33"/>
+      <c r="V6" s="33"/>
+    </row>
+    <row r="7" spans="1:22" ht="106.5">
+      <c r="A7" s="33">
+        <v>6388</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="37">
+        <v>1505000</v>
+      </c>
+      <c r="E7" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="38">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="33"/>
+      <c r="K7" s="43">
+        <v>0.5</v>
+      </c>
+      <c r="L7" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="33"/>
+      <c r="P7" s="33"/>
+      <c r="Q7" s="33"/>
+      <c r="R7" s="33"/>
+      <c r="S7" s="33"/>
+      <c r="T7" s="33"/>
+      <c r="U7" s="33"/>
+      <c r="V7" s="33"/>
+    </row>
+    <row r="8" spans="1:22" ht="45.75">
+      <c r="A8" s="33"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8" s="33">
+        <v>300000</v>
+      </c>
+      <c r="N8" s="33"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="33"/>
+      <c r="S8" s="33"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="33"/>
+      <c r="V8" s="33"/>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="A9" s="33"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="E9" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="38">
+        <v>2340000</v>
+      </c>
+      <c r="I9" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" s="33"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33"/>
+      <c r="P9" s="33"/>
+      <c r="Q9" s="33"/>
+      <c r="R9" s="33"/>
+      <c r="S9" s="33"/>
+      <c r="T9" s="33"/>
+      <c r="U9" s="33"/>
+      <c r="V9" s="33"/>
+    </row>
+    <row r="10" spans="1:22" ht="30.75">
+      <c r="A10" s="33"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="38">
         <v>1</v>
       </c>
-      <c r="I5" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="38"/>
-      <c r="L5" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-    </row>
-    <row r="6" spans="1:22" ht="121.5" customHeight="1">
-      <c r="A6" s="38"/>
-      <c r="B6" s="38"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="44" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="45">
-        <v>0</v>
-      </c>
-      <c r="H6" s="45">
-        <v>12</v>
-      </c>
-      <c r="I6" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" s="38"/>
-      <c r="L6" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="38"/>
-      <c r="T6" s="38"/>
-      <c r="U6" s="38"/>
-      <c r="V6" s="38"/>
-    </row>
-    <row r="7" spans="1:22" ht="106.5">
-      <c r="A7" s="38">
-        <v>6388</v>
-      </c>
-      <c r="B7" s="38" t="s">
+      <c r="I10" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="33"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="33"/>
+      <c r="U10" s="33"/>
+      <c r="V10" s="33"/>
+    </row>
+    <row r="11" spans="1:22" ht="30.75">
+      <c r="A11" s="33"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="M11" s="33"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="33"/>
+      <c r="R11" s="33"/>
+      <c r="S11" s="33"/>
+      <c r="T11" s="33"/>
+      <c r="U11" s="33"/>
+      <c r="V11" s="33"/>
+    </row>
+    <row r="12" spans="1:22" ht="91.5">
+      <c r="A12" s="33"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="M12" s="33"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="33"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="33"/>
+      <c r="S12" s="33"/>
+      <c r="T12" s="33"/>
+      <c r="U12" s="33"/>
+      <c r="V12" s="33"/>
+    </row>
+    <row r="13" spans="1:22" ht="30.75">
+      <c r="A13" s="33"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="42"/>
+      <c r="I13" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="M13" s="33"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="33"/>
+      <c r="P13" s="33"/>
+      <c r="Q13" s="33"/>
+      <c r="R13" s="33"/>
+      <c r="S13" s="33"/>
+      <c r="T13" s="33"/>
+      <c r="U13" s="33"/>
+      <c r="V13" s="33"/>
+    </row>
+    <row r="14" spans="1:22" ht="45.75">
+      <c r="A14" s="33"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="33"/>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="33"/>
+      <c r="S14" s="33"/>
+      <c r="T14" s="33"/>
+      <c r="U14" s="33"/>
+      <c r="V14" s="33"/>
+    </row>
+    <row r="15" spans="1:22" ht="60.75">
+      <c r="A15" s="33"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" s="38">
+        <v>2000</v>
+      </c>
+      <c r="I15" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="J15" s="33"/>
+      <c r="K15" s="43">
+        <v>0.5</v>
+      </c>
+      <c r="L15" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="M15" s="33"/>
+      <c r="N15" s="33"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="33"/>
+      <c r="R15" s="33"/>
+      <c r="S15" s="33"/>
+      <c r="T15" s="33"/>
+      <c r="U15" s="33"/>
+      <c r="V15" s="33"/>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="A16" s="33">
+        <v>6285</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="42">
-        <v>1505000</v>
-      </c>
-      <c r="E7" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="43">
+      <c r="D16" s="33">
+        <v>1777000</v>
+      </c>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38">
         <v>10000</v>
       </c>
-      <c r="I7" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="48">
-        <v>0.5</v>
-      </c>
-      <c r="L7" s="38" t="s">
+      <c r="I16" s="38"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="38"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="38"/>
-      <c r="V7" s="38"/>
-    </row>
-    <row r="8" spans="1:22" ht="45.75">
-      <c r="A8" s="38"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="43" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="M8" s="38">
-        <v>300000</v>
-      </c>
-      <c r="N8" s="38"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="38"/>
-      <c r="R8" s="38"/>
-      <c r="S8" s="38"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="38"/>
-    </row>
-    <row r="9" spans="1:22">
-      <c r="A9" s="38"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="43">
-        <v>2340000</v>
-      </c>
-      <c r="I9" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="M9" s="38"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="38"/>
-      <c r="P9" s="38"/>
-      <c r="Q9" s="38"/>
-      <c r="R9" s="38"/>
-      <c r="S9" s="38"/>
-      <c r="T9" s="38"/>
-      <c r="U9" s="38"/>
-      <c r="V9" s="38"/>
-    </row>
-    <row r="10" spans="1:22" ht="30.75">
-      <c r="A10" s="38"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" s="43">
-        <v>1</v>
-      </c>
-      <c r="I10" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="M10" s="38"/>
-      <c r="N10" s="38"/>
-      <c r="O10" s="38"/>
-      <c r="P10" s="38"/>
-      <c r="Q10" s="38"/>
-      <c r="R10" s="38"/>
-      <c r="S10" s="38"/>
-      <c r="T10" s="38"/>
-      <c r="U10" s="38"/>
-      <c r="V10" s="38"/>
-    </row>
-    <row r="11" spans="1:22" ht="30.75">
-      <c r="A11" s="38"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="43" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="38"/>
-      <c r="R11" s="38"/>
-      <c r="S11" s="38"/>
-      <c r="T11" s="38"/>
-      <c r="U11" s="38"/>
-      <c r="V11" s="38"/>
-    </row>
-    <row r="12" spans="1:22" ht="91.5">
-      <c r="A12" s="38"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43" t="s">
-        <v>50</v>
-      </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-    </row>
-    <row r="13" spans="1:22" ht="30.75">
-      <c r="A13" s="38"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" s="47"/>
-      <c r="I13" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="38"/>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="38"/>
-      <c r="S13" s="38"/>
-      <c r="T13" s="38"/>
-      <c r="U13" s="38"/>
-      <c r="V13" s="38"/>
-    </row>
-    <row r="14" spans="1:22" ht="45.75">
-      <c r="A14" s="38"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="43" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="L14" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="38"/>
-      <c r="P14" s="38"/>
-      <c r="Q14" s="38"/>
-      <c r="R14" s="38"/>
-      <c r="S14" s="38"/>
-      <c r="T14" s="38"/>
-      <c r="U14" s="38"/>
-      <c r="V14" s="38"/>
-    </row>
-    <row r="15" spans="1:22" ht="60.75">
-      <c r="A15" s="38"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="43" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="H15" s="43">
-        <v>2000</v>
-      </c>
-      <c r="I15" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="J15" s="38"/>
-      <c r="K15" s="48">
-        <v>0.5</v>
-      </c>
-      <c r="L15" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="38"/>
-      <c r="P15" s="38"/>
-      <c r="Q15" s="38"/>
-      <c r="R15" s="38"/>
-      <c r="S15" s="38"/>
-      <c r="T15" s="38"/>
-      <c r="U15" s="38"/>
-      <c r="V15" s="38"/>
-    </row>
-    <row r="16" spans="1:22">
-      <c r="A16" s="38">
-        <v>6285</v>
-      </c>
-      <c r="B16" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="38">
-        <v>1777000</v>
-      </c>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43">
-        <v>10000</v>
-      </c>
-      <c r="I16" s="43"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="38"/>
-      <c r="P16" s="38"/>
-      <c r="Q16" s="38"/>
-      <c r="R16" s="38"/>
-      <c r="S16" s="38"/>
-      <c r="T16" s="38"/>
-      <c r="U16" s="38"/>
-      <c r="V16" s="38"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="33"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="33"/>
+      <c r="V16" s="33"/>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="29"/>
@@ -1604,7 +1598,7 @@
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E7 E9:E22</xm:sqref>
+          <xm:sqref>E9:E22 E2:E7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1685,7 +1679,7 @@
         <v>1055099</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F2" s="20" t="s">
         <v>23</v>
@@ -1697,11 +1691,11 @@
       <c r="I2" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="32" t="s">
+      <c r="J2" s="44" t="s">
         <v>25</v>
       </c>
       <c r="K2" s="16"/>
-      <c r="L2" s="32" t="s">
+      <c r="L2" s="44" t="s">
         <v>26</v>
       </c>
       <c r="M2" s="16"/>
@@ -1715,7 +1709,7 @@
       <c r="C3" s="17"/>
       <c r="D3" s="16"/>
       <c r="E3" s="19" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F3" s="20" t="s">
         <v>28</v>
@@ -1729,9 +1723,9 @@
       <c r="I3" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="32"/>
+      <c r="J3" s="44"/>
       <c r="K3" s="16"/>
-      <c r="L3" s="32"/>
+      <c r="L3" s="44"/>
       <c r="M3" s="16"/>
     </row>
     <row r="4" spans="1:14" ht="45.75">
@@ -1740,7 +1734,7 @@
       <c r="C4" s="17"/>
       <c r="D4" s="16"/>
       <c r="E4" s="19" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F4" s="20" t="s">
         <v>29</v>
@@ -1754,9 +1748,9 @@
       <c r="I4" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="32"/>
+      <c r="J4" s="44"/>
       <c r="K4" s="16"/>
-      <c r="L4" s="32"/>
+      <c r="L4" s="44"/>
       <c r="M4" s="16"/>
     </row>
     <row r="5" spans="1:14" ht="91.5" customHeight="1">
@@ -1765,10 +1759,10 @@
       <c r="C5" s="17"/>
       <c r="D5" s="16"/>
       <c r="E5" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>30</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>31</v>
       </c>
       <c r="G5" s="21">
         <v>0</v>
@@ -1779,9 +1773,9 @@
       <c r="I5" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="32"/>
+      <c r="J5" s="44"/>
       <c r="K5" s="16"/>
-      <c r="L5" s="32"/>
+      <c r="L5" s="44"/>
       <c r="M5" s="16"/>
     </row>
     <row r="6" spans="1:14" ht="121.5" customHeight="1">
@@ -1790,10 +1784,10 @@
       <c r="C6" s="17"/>
       <c r="D6" s="16"/>
       <c r="E6" s="19" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6" s="21">
         <v>0</v>
@@ -1804,9 +1798,9 @@
       <c r="I6" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="32"/>
+      <c r="J6" s="44"/>
       <c r="K6" s="16"/>
-      <c r="L6" s="32"/>
+      <c r="L6" s="44"/>
       <c r="M6" s="16"/>
     </row>
     <row r="7" spans="1:14" ht="106.5">
@@ -1814,16 +1808,16 @@
         <v>6388</v>
       </c>
       <c r="B7" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>33</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>34</v>
       </c>
       <c r="D7" s="18">
         <v>1505000</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F7" s="23" t="s">
         <v>35</v>
@@ -1881,19 +1875,19 @@
       <c r="C9" s="16"/>
       <c r="D9" s="18"/>
       <c r="E9" s="19" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" s="24" t="s">
         <v>36</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J9" s="16"/>
       <c r="K9" s="16"/>
@@ -1908,10 +1902,10 @@
       <c r="C10" s="16"/>
       <c r="D10" s="18"/>
       <c r="E10" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" s="24" t="s">
         <v>36</v>
@@ -1935,7 +1929,7 @@
       <c r="C11" s="16"/>
       <c r="D11" s="18"/>
       <c r="E11" s="19" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F11" s="27" t="s">
         <v>48</v>
@@ -1960,7 +1954,7 @@
       <c r="C12" s="16"/>
       <c r="D12" s="18"/>
       <c r="E12" s="19" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F12" s="27" t="s">
         <v>49</v>
@@ -1985,7 +1979,7 @@
       <c r="C13" s="16"/>
       <c r="D13" s="18"/>
       <c r="E13" s="19" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>51</v>
@@ -2010,7 +2004,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="18"/>
       <c r="E14" s="19" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F14" s="27" t="s">
         <v>52</v>
@@ -2035,7 +2029,7 @@
       <c r="C15" s="16"/>
       <c r="D15" s="18"/>
       <c r="E15" s="19" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>53</v>
@@ -2066,7 +2060,7 @@
         <v>55</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" s="16">
         <v>1777000</v>
@@ -2176,7 +2170,7 @@
         <v>1055099</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>23</v>
@@ -2185,16 +2179,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="30.75">
       <c r="C3" s="2"/>
       <c r="E3" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>28</v>
@@ -2206,13 +2200,13 @@
         <v>20</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="30.75">
       <c r="C4" s="2"/>
       <c r="E4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>29</v>
@@ -2224,16 +2218,16 @@
         <v>25</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="91.5">
       <c r="C5" s="2"/>
       <c r="E5" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" s="7">
         <v>0</v>
@@ -2242,16 +2236,16 @@
         <v>1</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="121.5">
       <c r="C6" s="2"/>
       <c r="E6" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6" s="7">
         <v>0</v>
@@ -2260,7 +2254,7 @@
         <v>12</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="106.5">
@@ -2268,16 +2262,16 @@
         <v>6388</v>
       </c>
       <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
       </c>
       <c r="D7" s="9">
         <v>1505000</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>35</v>
@@ -2286,7 +2280,7 @@
         <v>36</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>37</v>
@@ -2295,7 +2289,7 @@
     <row r="8" spans="1:10" ht="45.75">
       <c r="D8" s="9"/>
       <c r="E8" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>40</v>
@@ -2304,52 +2298,52 @@
         <v>36</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="D9" s="9"/>
       <c r="E9" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>36</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="30.75">
       <c r="D10" s="9"/>
       <c r="E10" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>36</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="30.75">
       <c r="D11" s="9"/>
       <c r="E11" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>48</v>
@@ -2358,16 +2352,16 @@
         <v>36</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="121.5">
       <c r="D12" s="9"/>
       <c r="E12" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>49</v>
@@ -2376,16 +2370,16 @@
         <v>36</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="D13" s="9"/>
       <c r="E13" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>51</v>
@@ -2397,13 +2391,13 @@
         <v>28</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="45.75">
       <c r="D14" s="9"/>
       <c r="E14" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>52</v>
@@ -2412,16 +2406,16 @@
         <v>36</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="60.75">
       <c r="D15" s="9"/>
       <c r="E15" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>53</v>
@@ -2430,7 +2424,7 @@
         <v>36</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I15" s="12" t="s">
         <v>54</v>
@@ -2444,7 +2438,7 @@
         <v>55</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16">
         <v>1777000</v>
@@ -2487,160 +2481,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="33" t="s">
-        <v>70</v>
+      <c r="A2" s="45" t="s">
+        <v>71</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="33"/>
+      <c r="A3" s="45"/>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="33"/>
+      <c r="A4" s="45"/>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="34" t="s">
-        <v>76</v>
+      <c r="A5" s="46" t="s">
+        <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="34"/>
+      <c r="A6" s="46"/>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="34"/>
+      <c r="A7" s="46"/>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="34"/>
+      <c r="A8" s="46"/>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="34"/>
+      <c r="A9" s="46"/>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="35" t="s">
-        <v>86</v>
+      <c r="A10" s="47" t="s">
+        <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="35"/>
+      <c r="A11" s="47"/>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="36" t="s">
-        <v>91</v>
+      <c r="A12" s="48" t="s">
+        <v>92</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="36"/>
+      <c r="A13" s="48"/>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="36"/>
+      <c r="A14" s="48"/>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2655,12 +2649,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2913,18 +2909,16 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF06756A-F120-411C-9681-B6A6BBE09C5B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF437C67-40ED-4AFC-AAD6-8C1F78EC780A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2932,5 +2926,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF437C67-40ED-4AFC-AAD6-8C1F78EC780A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF06756A-F120-411C-9681-B6A6BBE09C5B}"/>
 </file>
--- a/01_Input/00_CO Validation/Serbia - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Serbia - Energy Projects.xlsx
@@ -1,18 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28619"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="264" documentId="11_8048FE8377A146D934E2F53C766C1D44588AAA59" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F51ACEDE-8BAD-4F61-BDBD-D40D3C0C4248}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="474" documentId="11_8048FE8377A146D934E2F53C766C1D44588AAA59" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60F0AF02-21F9-4AD1-8CFC-A98F7E7037E2}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="20" yWindow="740" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Projects (3)'!$A$1:$U$21</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -33,8 +41,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={65871F56-206B-45AB-826E-4DD840308F32}</author>
+  </authors>
+  <commentList>
+    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{65871F56-206B-45AB-826E-4DD840308F32}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    These 3 projects are part of the same platform but different donors and distinct projects.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="142">
   <si>
     <t>Project ID</t>
   </si>
@@ -130,7 +156,7 @@
     <t>Energy Efficiency in Buildings</t>
   </si>
   <si>
-    <t>PIMS+</t>
+    <t>https://co.pims.undp.org/project/view?id=6388</t>
   </si>
   <si>
     <t>Number of direct project beneficiaries disaggregated by gender (individual people)</t>
@@ -140,6 +166,9 @@
   </si>
   <si>
     <t xml:space="preserve">Among the beneficiaries were included the people using the buildings and benefitting from better thermal comfort as well as the people benefitting from project KM, training and new work opportunities. </t>
+  </si>
+  <si>
+    <t>GEF</t>
   </si>
   <si>
     <t>VF</t>
@@ -191,7 +220,85 @@
     <t>Circular Economy in Serbia</t>
   </si>
   <si>
-    <t>a network of around 10,000 stakeholders in order to foster co-operation and facilitate exchange experience and peer-to-peer learning</t>
+    <t>https://co.pims.undp.org/project/view?id=6285</t>
+  </si>
+  <si>
+    <t>Achieved 8250 direct beneficaries until June 30, 2024 (60% female)</t>
+  </si>
+  <si>
+    <t>Increase in installed renewable</t>
+  </si>
+  <si>
+    <t>0 MW</t>
+  </si>
+  <si>
+    <t>Achieved 12 MW until June 30, 2024</t>
+  </si>
+  <si>
+    <t>EU for Green Agenda in Serbia: Get started, Take action, Scale-up</t>
+  </si>
+  <si>
+    <t>https://www.undp.org/serbia/projects/eu-green-agenda-serbia</t>
+  </si>
+  <si>
+    <t>GHG and CO2 equivalent emission reduction / 1y (t CO2 eq)</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>7,011 tonnes of GHG and CO2 equivalent emission reduction per year</t>
+  </si>
+  <si>
+    <t>EU</t>
+  </si>
+  <si>
+    <t>RES installed capacities (solar PV-electicity, biomass, biogas and other)</t>
+  </si>
+  <si>
+    <t>1,139 kWth</t>
+  </si>
+  <si>
+    <t>Energy savings through implementation of EE improvement measures (TJ)</t>
+  </si>
+  <si>
+    <t>196 TJ of energy savings</t>
+  </si>
+  <si>
+    <t>Kilowatt hours saved through energy efficiency (EE) measures (KWh/year)</t>
+  </si>
+  <si>
+    <t>18,156,651 kWh/year saved through energy efficiency measures</t>
+  </si>
+  <si>
+    <t>Green Agenda in Serbia</t>
+  </si>
+  <si>
+    <t>1,278 tonnes of GHG and CO2 equivalent emission reduction per year</t>
+  </si>
+  <si>
+    <t>SDC</t>
+  </si>
+  <si>
+    <t>6,006 kWth</t>
+  </si>
+  <si>
+    <t>45 TJ of energy savings</t>
+  </si>
+  <si>
+    <t>3,516 tonnes of GHG and CO2 equivalent emission reduction per year</t>
+  </si>
+  <si>
+    <t>SECO</t>
+  </si>
+  <si>
+    <t>1,000 kWth</t>
+  </si>
+  <si>
+    <t>5,54 TJ of energy savings</t>
+  </si>
+  <si>
+    <t>1,538,400 kWh/year saved through energy efficiency measures</t>
   </si>
   <si>
     <t>Category</t>
@@ -219,6 +326,9 @@
   </si>
   <si>
     <t>Number of media outlets (newspaper, local and national TV, radio and other electronic media) informing the public about the EECGB Programme</t>
+  </si>
+  <si>
+    <t>PIMS+</t>
   </si>
   <si>
     <t xml:space="preserve">146 000
@@ -393,10 +503,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="[$€-2]\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -453,6 +565,14 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -480,7 +600,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -568,20 +688,114 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -610,7 +824,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -653,7 +867,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -692,6 +906,124 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -721,6 +1053,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Folashade Jaiyeola" id="{FDF7C1C6-6AA4-4120-B30F-B8937033BABF}" userId="S::folashade.jaiyeola@undp.org::c208a32e-6303-48b2-9538-645490e99643" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1008,10 +1346,18 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B11" dT="2024-11-25T20:38:55.82" personId="{FDF7C1C6-6AA4-4120-B30F-B8937033BABF}" id="{65871F56-206B-45AB-826E-4DD840308F32}">
+    <text>These 3 projects are part of the same platform but different donors and distinct projects.</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B60595EA-59F6-474E-B152-583725599006}">
-  <dimension ref="A1:Z11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B60595EA-59F6-474E-B152-583725599006}">
+  <dimension ref="A1:Z22"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="43.42578125" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
@@ -1030,7 +1376,7 @@
     <col min="21" max="21" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="45.75">
+    <row r="1" spans="1:26" ht="43.5">
       <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
@@ -1156,7 +1502,7 @@
       <c r="B3" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="48" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="35">
@@ -1177,12 +1523,14 @@
       <c r="I3" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="33"/>
+      <c r="J3" s="33" t="s">
+        <v>35</v>
+      </c>
       <c r="K3" s="39">
         <v>0.5</v>
       </c>
       <c r="L3" s="46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M3" s="30"/>
       <c r="N3" s="47" t="s">
@@ -1196,7 +1544,7 @@
       <c r="T3" s="30"/>
       <c r="U3" s="23"/>
       <c r="X3" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y3" s="33"/>
       <c r="Z3" s="33"/>
@@ -1207,24 +1555,26 @@
       <c r="C4" s="33"/>
       <c r="D4" s="35"/>
       <c r="E4" s="33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="33" t="s">
-        <v>38</v>
+      <c r="H4" s="67" t="s">
+        <v>39</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="33"/>
+        <v>40</v>
+      </c>
+      <c r="J4" s="33" t="s">
+        <v>35</v>
+      </c>
       <c r="K4" s="33"/>
       <c r="L4" s="46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M4" s="30"/>
       <c r="N4" s="47" t="s">
@@ -1238,22 +1588,22 @@
       <c r="T4" s="30"/>
       <c r="U4" s="23"/>
       <c r="X4" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y4" s="33">
         <v>300000</v>
       </c>
       <c r="Z4" s="33"/>
     </row>
-    <row r="5" spans="1:26" ht="30.75">
+    <row r="5" spans="1:26" ht="29.1">
       <c r="A5" s="33"/>
       <c r="B5" s="33"/>
       <c r="C5" s="33"/>
       <c r="E5" s="35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G5" s="36" t="s">
         <v>33</v>
@@ -1262,12 +1612,14 @@
         <v>2340000</v>
       </c>
       <c r="I5" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="33"/>
+        <v>43</v>
+      </c>
+      <c r="J5" s="33" t="s">
+        <v>35</v>
+      </c>
       <c r="K5" s="33"/>
       <c r="L5" s="46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M5" s="30"/>
       <c r="N5" s="47" t="s">
@@ -1281,21 +1633,21 @@
       <c r="T5" s="30"/>
       <c r="U5" s="23"/>
       <c r="X5" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y5" s="33"/>
       <c r="Z5" s="33"/>
     </row>
-    <row r="6" spans="1:26" ht="30.75">
+    <row r="6" spans="1:26" ht="29.1">
       <c r="A6" s="33"/>
       <c r="B6" s="33"/>
       <c r="C6" s="33"/>
       <c r="D6" s="35"/>
       <c r="E6" s="33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6" s="36" t="s">
         <v>33</v>
@@ -1304,12 +1656,14 @@
         <v>1</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="33"/>
+        <v>40</v>
+      </c>
+      <c r="J6" s="33" t="s">
+        <v>35</v>
+      </c>
       <c r="K6" s="33"/>
       <c r="L6" s="46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M6" s="30"/>
       <c r="N6" s="47" t="s">
@@ -1320,24 +1674,24 @@
       <c r="Q6" s="30"/>
       <c r="R6" s="30"/>
       <c r="S6" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T6" s="30"/>
       <c r="U6" s="23"/>
       <c r="X6" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y6" s="33"/>
       <c r="Z6" s="33"/>
     </row>
-    <row r="7" spans="1:26" ht="30.75">
+    <row r="7" spans="1:26" ht="29.1">
       <c r="A7" s="33"/>
       <c r="B7" s="33"/>
       <c r="C7" s="33"/>
       <c r="D7" s="35"/>
       <c r="E7" s="33"/>
       <c r="F7" s="33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G7" s="36" t="s">
         <v>33</v>
@@ -1346,12 +1700,14 @@
         <v>6500</v>
       </c>
       <c r="I7" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="33"/>
+        <v>40</v>
+      </c>
+      <c r="J7" s="33" t="s">
+        <v>35</v>
+      </c>
       <c r="K7" s="33"/>
       <c r="L7" s="46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M7" s="30"/>
       <c r="N7" s="47" t="s">
@@ -1365,21 +1721,21 @@
       <c r="T7" s="30"/>
       <c r="U7" s="23"/>
       <c r="X7" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y7" s="33"/>
       <c r="Z7" s="33"/>
     </row>
-    <row r="8" spans="1:26" ht="60.75">
+    <row r="8" spans="1:26" ht="57.95">
       <c r="A8" s="33"/>
       <c r="B8" s="33"/>
       <c r="C8" s="33"/>
       <c r="D8" s="35"/>
       <c r="E8" s="33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" s="36" t="s">
         <v>33</v>
@@ -1388,14 +1744,16 @@
         <v>2000</v>
       </c>
       <c r="I8" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="33"/>
+        <v>50</v>
+      </c>
+      <c r="J8" s="33" t="s">
+        <v>35</v>
+      </c>
       <c r="K8" s="39">
         <v>0.5</v>
       </c>
       <c r="L8" s="46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M8" s="30"/>
       <c r="N8" s="47" t="s">
@@ -1409,39 +1767,47 @@
       <c r="T8" s="30"/>
       <c r="U8" s="23"/>
       <c r="X8" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y8" s="33"/>
       <c r="Z8" s="33"/>
     </row>
-    <row r="9" spans="1:26" ht="76.5">
-      <c r="A9" s="33">
+    <row r="9" spans="1:26" ht="45.75">
+      <c r="A9" s="68">
         <v>6285</v>
       </c>
-      <c r="B9" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="33">
+      <c r="B9" s="68" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="72">
         <v>1777000</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
+        <v>48</v>
+      </c>
+      <c r="F9" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="33">
+        <v>0</v>
+      </c>
       <c r="H9" s="33">
         <v>10000</v>
       </c>
       <c r="I9" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
+        <v>53</v>
+      </c>
+      <c r="J9" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="39">
+        <v>0.5</v>
+      </c>
       <c r="L9" s="46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M9" s="30"/>
       <c r="N9" s="47" t="s">
@@ -1455,20 +1821,408 @@
       <c r="T9" s="30"/>
       <c r="U9" s="23"/>
       <c r="X9" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y9" s="33"/>
       <c r="Z9" s="33"/>
     </row>
-    <row r="11" spans="1:26">
-      <c r="A11" s="27"/>
+    <row r="10" spans="1:26" ht="30.75">
+      <c r="A10" s="69"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="73"/>
+      <c r="F10" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10">
+        <v>12</v>
+      </c>
+      <c r="I10" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="N10" s="47" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="45.75">
+      <c r="A11" s="82">
+        <v>127312</v>
+      </c>
+      <c r="B11" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="76" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="85">
+        <v>7200000</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="L11" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="47" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="29.1">
+      <c r="A12" s="74"/>
+      <c r="B12" s="83"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="86"/>
+      <c r="E12" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="L12" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="47" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="29.1">
+      <c r="A13" s="74"/>
+      <c r="B13" s="83"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="86"/>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="L13" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" s="47" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" s="56" customFormat="1" ht="29.1">
+      <c r="A14" s="75"/>
+      <c r="B14" s="84"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="56" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="57" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" s="57" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14" s="58" t="s">
+        <v>62</v>
+      </c>
+      <c r="L14" s="59" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" s="60" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="41.1" customHeight="1">
+      <c r="A15" s="74">
+        <v>129089</v>
+      </c>
+      <c r="B15" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="81" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="79">
+        <v>4905556</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="61" t="s">
+        <v>70</v>
+      </c>
+      <c r="J15" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="L15" s="51" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="29.1">
+      <c r="A16" s="74"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="81"/>
+      <c r="D16" s="79"/>
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I16" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="J16" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="L16" s="51" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="56" customFormat="1" ht="29.1">
+      <c r="A17" s="74"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="56" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="57" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="J17" s="58" t="s">
+        <v>71</v>
+      </c>
+      <c r="L17" s="59" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="43.5">
+      <c r="A18" s="74">
+        <v>132184</v>
+      </c>
+      <c r="B18" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="76" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="79">
+        <v>2222222</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I18" s="54" t="s">
+        <v>74</v>
+      </c>
+      <c r="J18" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="L18" s="51" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="29.1">
+      <c r="A19" s="74"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="79"/>
+      <c r="E19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I19" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="J19" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="L19" s="51" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="29.1">
+      <c r="A20" s="74"/>
+      <c r="B20" s="74"/>
+      <c r="C20" s="77"/>
+      <c r="D20" s="79"/>
+      <c r="E20" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I20" t="s">
+        <v>77</v>
+      </c>
+      <c r="J20" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="L20" s="51" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="56" customFormat="1" ht="29.1">
+      <c r="A21" s="75"/>
+      <c r="B21" s="75"/>
+      <c r="C21" s="78"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="56" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" s="57" t="s">
+        <v>67</v>
+      </c>
+      <c r="G21" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="H21" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="I21" s="63" t="s">
+        <v>78</v>
+      </c>
+      <c r="J21" s="58" t="s">
+        <v>75</v>
+      </c>
+      <c r="L21" s="59" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="52"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="62"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="64"/>
+      <c r="L22" s="52"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:U21" xr:uid="{B60595EA-59F6-474E-B152-583725599006}"/>
+  <mergeCells count="16">
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="D18:D21"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D11:D14"/>
+  </mergeCells>
   <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q9" xr:uid="{E6FFE709-7971-4C32-A2AC-463594632CCD}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N9" xr:uid="{108784E4-1C63-460E-A7ED-E941E787ACD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N14" xr:uid="{108784E4-1C63-460E-A7ED-E941E787ACD6}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O9" xr:uid="{52E1A357-B5A0-4ED8-B137-496AA3D4802B}">
@@ -1495,8 +2249,15 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{93EC6422-B7DE-4C5B-B8D7-4A6CF7F1AEB5}"/>
+    <hyperlink ref="C9" r:id="rId2" xr:uid="{16E5BD58-AF80-40A7-8AD1-49A2F4930AC2}"/>
+    <hyperlink ref="C3" r:id="rId3" xr:uid="{11DAA5E2-60AE-4129-A5E3-A8297EE515AF}"/>
+    <hyperlink ref="C11" r:id="rId4" xr:uid="{C9E4B838-BFDC-4D5B-8397-142116D0D60D}"/>
+    <hyperlink ref="C15" r:id="rId5" xr:uid="{84428103-228E-409F-BA86-38C868651DC6}"/>
+    <hyperlink ref="C18" r:id="rId6" xr:uid="{773AD667-2F3D-45EF-84DB-56BC2B75D1F1}"/>
+    <hyperlink ref="C9:C10" r:id="rId7" display="https://co.pims.undp.org/project/view?id=6285" xr:uid="{EA3778F0-A753-455F-AC7A-C77D7A09A75A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId8"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -1504,7 +2265,7 @@
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>E10:E15</xm:sqref>
+          <xm:sqref>E11:E22</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7B4CDD62-ABAA-4742-8902-7B6FCAF7865A}">
           <x14:formula1>
@@ -1521,7 +2282,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C86E5308-F14E-4D09-97CE-0ADFEAA0A16D}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="43.42578125" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
@@ -1568,13 +2329,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="12" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="N1" s="28" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="60.75" customHeight="1">
@@ -1594,7 +2355,7 @@
         <v>23</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="G2" s="19">
         <v>0</v>
@@ -1603,11 +2364,11 @@
       <c r="I2" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="48" t="s">
+      <c r="J2" s="88" t="s">
         <v>26</v>
       </c>
       <c r="K2" s="14"/>
-      <c r="L2" s="48" t="s">
+      <c r="L2" s="88" t="s">
         <v>27</v>
       </c>
       <c r="M2" s="14"/>
@@ -1615,7 +2376,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="45.75">
+    <row r="3" spans="1:14" ht="43.5">
       <c r="A3" s="14"/>
       <c r="B3" s="14"/>
       <c r="C3" s="15"/>
@@ -1624,7 +2385,7 @@
         <v>23</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="G3" s="19">
         <v>3</v>
@@ -1635,12 +2396,12 @@
       <c r="I3" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="48"/>
+      <c r="J3" s="88"/>
       <c r="K3" s="14"/>
-      <c r="L3" s="48"/>
+      <c r="L3" s="88"/>
       <c r="M3" s="14"/>
     </row>
-    <row r="4" spans="1:14" ht="45.75">
+    <row r="4" spans="1:14" ht="43.5">
       <c r="A4" s="14"/>
       <c r="B4" s="14"/>
       <c r="C4" s="15"/>
@@ -1649,7 +2410,7 @@
         <v>23</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="G4" s="19">
         <v>0</v>
@@ -1660,9 +2421,9 @@
       <c r="I4" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="48"/>
+      <c r="J4" s="88"/>
       <c r="K4" s="14"/>
-      <c r="L4" s="48"/>
+      <c r="L4" s="88"/>
       <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:14" ht="91.5" customHeight="1">
@@ -1671,10 +2432,10 @@
       <c r="C5" s="15"/>
       <c r="D5" s="14"/>
       <c r="E5" s="17" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="G5" s="19">
         <v>0</v>
@@ -1685,9 +2446,9 @@
       <c r="I5" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="48"/>
+      <c r="J5" s="88"/>
       <c r="K5" s="14"/>
-      <c r="L5" s="48"/>
+      <c r="L5" s="88"/>
       <c r="M5" s="14"/>
     </row>
     <row r="6" spans="1:14" ht="121.5" customHeight="1">
@@ -1696,10 +2457,10 @@
       <c r="C6" s="15"/>
       <c r="D6" s="14"/>
       <c r="E6" s="17" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -1710,12 +2471,12 @@
       <c r="I6" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="48"/>
+      <c r="J6" s="88"/>
       <c r="K6" s="14"/>
-      <c r="L6" s="48"/>
+      <c r="L6" s="88"/>
       <c r="M6" s="14"/>
     </row>
-    <row r="7" spans="1:14" ht="106.5">
+    <row r="7" spans="1:14" ht="87">
       <c r="A7" s="14">
         <v>6388</v>
       </c>
@@ -1723,7 +2484,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="D7" s="16">
         <v>1505000</v>
@@ -1748,34 +2509,34 @@
         <v>0.5</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M7" s="14"/>
     </row>
-    <row r="8" spans="1:14" ht="45.75">
+    <row r="8" spans="1:14" ht="43.5">
       <c r="A8" s="14"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="16"/>
       <c r="E8" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" s="22" t="s">
         <v>33</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
       <c r="L8" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M8" s="14">
         <v>300000</v>
@@ -1790,34 +2551,34 @@
         <v>23</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" s="22" t="s">
         <v>33</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J9" s="14"/>
       <c r="K9" s="14"/>
       <c r="L9" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M9" s="14"/>
     </row>
-    <row r="10" spans="1:14" ht="30.75">
+    <row r="10" spans="1:14" ht="29.1">
       <c r="A10" s="14"/>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
       <c r="D10" s="16"/>
       <c r="E10" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" s="22" t="s">
         <v>33</v>
@@ -1826,16 +2587,16 @@
         <v>1</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J10" s="14"/>
       <c r="K10" s="14"/>
       <c r="L10" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M10" s="14"/>
     </row>
-    <row r="11" spans="1:14" ht="30.75">
+    <row r="11" spans="1:14" ht="29.1">
       <c r="A11" s="14"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -1844,23 +2605,23 @@
         <v>19</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="G11" s="22" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="21"/>
       <c r="I11" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
       <c r="L11" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M11" s="14"/>
     </row>
-    <row r="12" spans="1:14" ht="91.5">
+    <row r="12" spans="1:14" ht="87">
       <c r="A12" s="14"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
@@ -1869,23 +2630,23 @@
         <v>23</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="G12" s="22" t="s">
         <v>33</v>
       </c>
       <c r="H12" s="21"/>
       <c r="I12" s="21" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="14"/>
       <c r="L12" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M12" s="14"/>
     </row>
-    <row r="13" spans="1:14" ht="30.75">
+    <row r="13" spans="1:14" ht="29.1">
       <c r="A13" s="14"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -1894,23 +2655,23 @@
         <v>23</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="G13" s="22" t="s">
         <v>33</v>
       </c>
       <c r="H13" s="26"/>
       <c r="I13" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J13" s="14"/>
       <c r="K13" s="14"/>
       <c r="L13" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M13" s="14"/>
     </row>
-    <row r="14" spans="1:14" ht="45.75">
+    <row r="14" spans="1:14" ht="43.5">
       <c r="A14" s="14"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -1919,32 +2680,32 @@
         <v>23</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="G14" s="22" t="s">
         <v>33</v>
       </c>
       <c r="H14" s="21"/>
       <c r="I14" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J14" s="14"/>
       <c r="K14" s="14"/>
       <c r="L14" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M14" s="14"/>
     </row>
-    <row r="15" spans="1:14" ht="60.75">
+    <row r="15" spans="1:14" ht="57.95">
       <c r="A15" s="14"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="16"/>
       <c r="E15" s="17" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G15" s="22" t="s">
         <v>33</v>
@@ -1953,14 +2714,14 @@
         <v>2000</v>
       </c>
       <c r="I15" s="21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J15" s="14"/>
       <c r="K15" s="24">
         <v>0.5</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M15" s="14"/>
     </row>
@@ -1969,10 +2730,10 @@
         <v>6285</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="D16" s="14">
         <v>1777000</v>
@@ -1987,7 +2748,7 @@
       <c r="J16" s="14"/>
       <c r="K16" s="14"/>
       <c r="L16" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M16" s="14"/>
     </row>
@@ -2024,7 +2785,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="43.42578125" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
@@ -2068,7 +2829,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="60.75">
+    <row r="2" spans="1:10" ht="29.1">
       <c r="A2">
         <v>122808</v>
       </c>
@@ -2082,28 +2843,28 @@
         <v>1055099</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="G2" s="5">
         <v>0</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="30.75">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="29.1">
       <c r="C3" s="2"/>
       <c r="E3" s="3" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
@@ -2112,16 +2873,16 @@
         <v>20</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="30.75">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="29.1">
       <c r="C4" s="2"/>
       <c r="E4" s="3" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="G4" s="5">
         <v>0</v>
@@ -2130,16 +2891,16 @@
         <v>25</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="91.5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.5">
       <c r="C5" s="2"/>
       <c r="E5" s="3" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="G5" s="5">
         <v>0</v>
@@ -2148,16 +2909,16 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="121.5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="57.95">
       <c r="C6" s="2"/>
       <c r="E6" s="3" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="G6" s="5">
         <v>0</v>
@@ -2166,10 +2927,10 @@
         <v>12</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="106.5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="87">
       <c r="A7">
         <v>6388</v>
       </c>
@@ -2177,13 +2938,13 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="D7" s="7">
         <v>1505000</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>32</v>
@@ -2192,109 +2953,109 @@
         <v>33</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="45.75">
+    <row r="8" spans="1:10" ht="43.5">
       <c r="D8" s="7"/>
       <c r="E8" s="3" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="D9" s="7"/>
       <c r="E9" s="3" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="30.75">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="29.1">
       <c r="D10" s="7"/>
       <c r="E10" s="3" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="30.75">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="29.1">
       <c r="D11" s="7"/>
       <c r="E11" s="3" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="121.5">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="116.1">
       <c r="D12" s="7"/>
       <c r="E12" s="3" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="D13" s="7"/>
       <c r="E13" s="3" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>33</v>
@@ -2303,43 +3064,43 @@
         <v>28</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="45.75">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="43.5">
       <c r="D14" s="7"/>
       <c r="E14" s="3" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="60.75">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="57.95">
       <c r="D15" s="7"/>
       <c r="E15" s="3" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>33</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2347,10 +3108,10 @@
         <v>6285</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="D16">
         <v>1777000</v>
@@ -2386,7 +3147,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="2" width="52.7109375" customWidth="1"/>
   </cols>
@@ -2399,172 +3160,172 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="49" t="s">
-        <v>78</v>
+    <row r="2" spans="1:2" ht="43.5">
+      <c r="A2" s="89" t="s">
+        <v>106</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="49" t="s">
-        <v>43</v>
+      <c r="A3" s="89" t="s">
+        <v>44</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="49" t="s">
-        <v>81</v>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="29.1">
+      <c r="A4" s="89" t="s">
+        <v>109</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="49" t="s">
-        <v>83</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="29.1">
+      <c r="A5" s="89" t="s">
+        <v>111</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="49" t="s">
-        <v>85</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="87">
+      <c r="A6" s="89" t="s">
+        <v>113</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="49" t="s">
-        <v>87</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="43.5">
+      <c r="A7" s="89" t="s">
+        <v>115</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="49" t="s">
-        <v>89</v>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="43.5">
+      <c r="A8" s="89" t="s">
+        <v>117</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="49" t="s">
-        <v>91</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="43.5">
+      <c r="A9" s="89" t="s">
+        <v>119</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="B10" s="50" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="50" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="49" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="29.1">
+      <c r="A10" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="90" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="29.1">
+      <c r="A11" s="89" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="90" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="43.5">
+      <c r="A12" s="89" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="41" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="29.1">
+      <c r="A13" s="89" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="90" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="89" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="90" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="29.1">
+      <c r="A15" s="89" t="s">
+        <v>129</v>
+      </c>
+      <c r="B15" s="90" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="29.1">
+      <c r="A16" s="89" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="90" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="29.1">
+      <c r="A17" s="89" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="29.1">
+      <c r="A18" s="89" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="90" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="72.599999999999994">
+      <c r="A19" s="89" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" s="90" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="29.1">
+      <c r="A20" s="89" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="90" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="43.5">
+      <c r="A21" s="89" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="91" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="29.1">
+      <c r="A22" s="89" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="41" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="50" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="B14" s="50" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="49" t="s">
-        <v>101</v>
-      </c>
-      <c r="B15" s="50" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="B16" s="50" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="41" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="B18" s="50" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="49" t="s">
-        <v>108</v>
-      </c>
-      <c r="B19" s="50" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="49" t="s">
-        <v>110</v>
-      </c>
-      <c r="B20" s="50" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="51" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" s="50" t="s">
-        <v>113</v>
+      <c r="B22" s="90" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -2573,6 +3334,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
@@ -2583,18 +3353,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -2619,6 +3380,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2698,6 +3460,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -2842,13 +3609,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF06756A-F120-411C-9681-B6A6BBE09C5B}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF437C67-40ED-4AFC-AAD6-8C1F78EC780A}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF06756A-F120-411C-9681-B6A6BBE09C5B}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D2A1C50-1C6D-4FD2-8E6E-E954BFAF8FB5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{726FAFA1-4912-493A-A6C8-CCDAC2F47FA4}"/>
 </file>
--- a/01_Input/00_CO Validation/Serbia - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Serbia - Energy Projects.xlsx
@@ -337,7 +337,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -599,7 +599,6 @@
     <xf numFmtId="165" fontId="0" fillId="5" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1688,14 +1687,6 @@
       <c r="AC9" s="33" t="n"/>
     </row>
     <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="97" t="n"/>
-      <c r="B10" s="97" t="n"/>
-      <c r="C10" s="97" t="n"/>
-      <c r="D10" s="97" t="n"/>
-      <c r="E10" s="97" t="n"/>
-      <c r="F10" s="97" t="n"/>
-      <c r="G10" s="97" t="n"/>
-      <c r="H10" s="97" t="n"/>
       <c r="J10" s="49" t="inlineStr">
         <is>
           <t>Increase in installed renewable</t>
@@ -1726,26 +1717,26 @@
       </c>
     </row>
     <row r="11" ht="45.75" customHeight="1">
-      <c r="A11" s="98" t="n">
+      <c r="A11" s="97" t="n">
         <v>127312</v>
       </c>
-      <c r="B11" s="99" t="inlineStr">
+      <c r="B11" s="98" t="inlineStr">
         <is>
           <t>EU for Green Agenda in Serbia: Get started, Take action, Scale-up</t>
         </is>
       </c>
-      <c r="C11" s="100" t="inlineStr">
+      <c r="C11" s="99" t="inlineStr">
         <is>
           <t>https://www.undp.org/serbia/projects/eu-green-agenda-serbia</t>
         </is>
       </c>
-      <c r="D11" s="101" t="n">
+      <c r="D11" s="100" t="n">
         <v>7200000</v>
       </c>
-      <c r="E11" s="102" t="n"/>
-      <c r="F11" s="102" t="n"/>
-      <c r="G11" s="102" t="n"/>
-      <c r="H11" s="101" t="inlineStr">
+      <c r="E11" s="101" t="n"/>
+      <c r="F11" s="101" t="n"/>
+      <c r="G11" s="101" t="n"/>
+      <c r="H11" s="100" t="inlineStr">
         <is>
           <t>Non-VF</t>
         </is>
@@ -1861,14 +1852,6 @@
       </c>
     </row>
     <row r="14" ht="29.1" customFormat="1" customHeight="1" s="56">
-      <c r="A14" s="56" t="n"/>
-      <c r="B14" s="56" t="n"/>
-      <c r="C14" s="56" t="n"/>
-      <c r="D14" s="56" t="n"/>
-      <c r="E14" s="56" t="n"/>
-      <c r="F14" s="56" t="n"/>
-      <c r="G14" s="56" t="n"/>
-      <c r="H14" s="56" t="n"/>
       <c r="I14" s="56" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
@@ -1919,13 +1902,13 @@
           <t>https://www.undp.org/serbia/projects/eu-green-agenda-serbia</t>
         </is>
       </c>
-      <c r="D15" s="103" t="n">
+      <c r="D15" s="102" t="n">
         <v>4905556</v>
       </c>
-      <c r="E15" s="104" t="n"/>
-      <c r="F15" s="104" t="n"/>
-      <c r="G15" s="104" t="n"/>
-      <c r="H15" s="103" t="inlineStr">
+      <c r="E15" s="103" t="n"/>
+      <c r="F15" s="103" t="n"/>
+      <c r="G15" s="103" t="n"/>
+      <c r="H15" s="102" t="inlineStr">
         <is>
           <t>Non-VF</t>
         </is>
@@ -1994,12 +1977,6 @@
       </c>
     </row>
     <row r="17" ht="29.1" customFormat="1" customHeight="1" s="56">
-      <c r="C17" s="97" t="n"/>
-      <c r="D17" s="56" t="n"/>
-      <c r="E17" s="56" t="n"/>
-      <c r="F17" s="56" t="n"/>
-      <c r="G17" s="56" t="n"/>
-      <c r="H17" s="56" t="n"/>
       <c r="I17" s="56" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
@@ -2040,18 +2017,18 @@
           <t>Green Agenda in Serbia</t>
         </is>
       </c>
-      <c r="C18" s="100" t="inlineStr">
+      <c r="C18" s="99" t="inlineStr">
         <is>
           <t>https://www.undp.org/serbia/projects/eu-green-agenda-serbia</t>
         </is>
       </c>
-      <c r="D18" s="103" t="n">
+      <c r="D18" s="102" t="n">
         <v>2222222</v>
       </c>
-      <c r="E18" s="104" t="n"/>
-      <c r="F18" s="104" t="n"/>
-      <c r="G18" s="104" t="n"/>
-      <c r="H18" s="103" t="inlineStr">
+      <c r="E18" s="103" t="n"/>
+      <c r="F18" s="103" t="n"/>
+      <c r="G18" s="103" t="n"/>
+      <c r="H18" s="102" t="inlineStr">
         <is>
           <t>Non-VF</t>
         </is>
@@ -2152,14 +2129,6 @@
       </c>
     </row>
     <row r="21" ht="29.1" customFormat="1" customHeight="1" s="56">
-      <c r="A21" s="56" t="n"/>
-      <c r="B21" s="56" t="n"/>
-      <c r="C21" s="56" t="n"/>
-      <c r="D21" s="56" t="n"/>
-      <c r="E21" s="56" t="n"/>
-      <c r="F21" s="56" t="n"/>
-      <c r="G21" s="56" t="n"/>
-      <c r="H21" s="56" t="n"/>
       <c r="I21" s="56" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
@@ -2195,11 +2164,11 @@
       <c r="A22" s="74" t="n"/>
       <c r="B22" s="74" t="n"/>
       <c r="C22" s="77" t="n"/>
-      <c r="D22" s="105" t="n"/>
-      <c r="E22" s="105" t="n"/>
-      <c r="F22" s="105" t="n"/>
-      <c r="G22" s="105" t="n"/>
-      <c r="H22" s="105" t="n"/>
+      <c r="D22" s="104" t="n"/>
+      <c r="E22" s="104" t="n"/>
+      <c r="F22" s="104" t="n"/>
+      <c r="G22" s="104" t="n"/>
+      <c r="H22" s="104" t="n"/>
       <c r="J22" s="65" t="n"/>
       <c r="K22" s="83" t="n"/>
       <c r="L22" s="83" t="n"/>
@@ -2208,25 +2177,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:U21"/>
-  <mergeCells count="16">
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D18:D21"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="C18:C21"/>
-  </mergeCells>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="Q2:Q9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -2253,12 +2204,6 @@
     </dataValidation>
     <dataValidation sqref="S2:S9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
@@ -2450,9 +2395,9 @@
 of the Central Government Buildings (6000)</t>
         </is>
       </c>
-      <c r="J3" s="106" t="n"/>
+      <c r="J3" s="105" t="n"/>
       <c r="K3" s="14" t="n"/>
-      <c r="L3" s="106" t="n"/>
+      <c r="L3" s="105" t="n"/>
       <c r="M3" s="14" t="n"/>
     </row>
     <row r="4" ht="43.5" customHeight="1">
@@ -2482,9 +2427,9 @@
 of the Central Government Buildings (6000)</t>
         </is>
       </c>
-      <c r="J4" s="106" t="n"/>
+      <c r="J4" s="105" t="n"/>
       <c r="K4" s="14" t="n"/>
-      <c r="L4" s="106" t="n"/>
+      <c r="L4" s="105" t="n"/>
       <c r="M4" s="14" t="n"/>
     </row>
     <row r="5" ht="91.5" customHeight="1">
@@ -2514,9 +2459,9 @@
 of the Central Government Buildings (6000)</t>
         </is>
       </c>
-      <c r="J5" s="106" t="n"/>
+      <c r="J5" s="105" t="n"/>
       <c r="K5" s="14" t="n"/>
-      <c r="L5" s="106" t="n"/>
+      <c r="L5" s="105" t="n"/>
       <c r="M5" s="14" t="n"/>
     </row>
     <row r="6" ht="121.5" customHeight="1">
@@ -2546,9 +2491,9 @@
 of the Central Government Buildings (6000)</t>
         </is>
       </c>
-      <c r="J6" s="107" t="n"/>
+      <c r="J6" s="106" t="n"/>
       <c r="K6" s="14" t="n"/>
-      <c r="L6" s="107" t="n"/>
+      <c r="L6" s="106" t="n"/>
       <c r="M6" s="14" t="n"/>
     </row>
     <row r="7" ht="87" customHeight="1">
@@ -3482,288 +3427,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="108" t="inlineStr">
+      <c r="A1" s="107" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="108" t="inlineStr">
+      <c r="B1" s="107" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
     </row>
     <row r="2" ht="43.5" customHeight="1">
-      <c r="A2" s="109" t="inlineStr">
+      <c r="A2" s="108" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="B2" s="109" t="inlineStr">
+      <c r="B2" s="108" t="inlineStr">
         <is>
           <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="109" t="inlineStr">
+      <c r="A3" s="108" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="B3" s="109" t="inlineStr">
+      <c r="B3" s="108" t="inlineStr">
         <is>
           <t>Installed renewable or clean-energy power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="29.1" customHeight="1">
-      <c r="A4" s="109" t="inlineStr">
+      <c r="A4" s="108" t="inlineStr">
         <is>
           <t>Energy Storage (MW)</t>
         </is>
       </c>
-      <c r="B4" s="109" t="inlineStr">
+      <c r="B4" s="108" t="inlineStr">
         <is>
           <t>Installed energy storage power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="29.1" customHeight="1">
-      <c r="A5" s="109" t="inlineStr">
+      <c r="A5" s="108" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="B5" s="109" t="inlineStr">
+      <c r="B5" s="108" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="87" customHeight="1">
-      <c r="A6" s="109" t="inlineStr">
+      <c r="A6" s="108" t="inlineStr">
         <is>
           <t>Clean Heating</t>
         </is>
       </c>
-      <c r="B6" s="109" t="inlineStr">
+      <c r="B6" s="108" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="43.5" customHeight="1">
-      <c r="A7" s="109" t="inlineStr">
+      <c r="A7" s="108" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="B7" s="109" t="inlineStr">
+      <c r="B7" s="108" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean, affordable, and sustainable energy for agricultural and food-system activities.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="43.5" customHeight="1">
-      <c r="A8" s="109" t="inlineStr">
+      <c r="A8" s="108" t="inlineStr">
         <is>
           <t>Health Services</t>
         </is>
       </c>
-      <c r="B8" s="109" t="inlineStr">
+      <c r="B8" s="108" t="inlineStr">
         <is>
           <t>Number of people who gain access to health care facilities through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="43.5" customHeight="1">
-      <c r="A9" s="109" t="inlineStr">
+      <c r="A9" s="108" t="inlineStr">
         <is>
           <t>Water Services</t>
         </is>
       </c>
-      <c r="B9" s="109" t="inlineStr">
+      <c r="B9" s="108" t="inlineStr">
         <is>
           <t>Number of people who gain access to water services through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="29.1" customHeight="1">
-      <c r="A10" s="109" t="inlineStr">
+      <c r="A10" s="108" t="inlineStr">
         <is>
           <t>Education Services</t>
         </is>
       </c>
-      <c r="B10" s="109" t="inlineStr">
+      <c r="B10" s="108" t="inlineStr">
         <is>
           <t>Number of people who gain access to education services through clean energy systems, including students and teachers.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="29.1" customHeight="1">
-      <c r="A11" s="109" t="inlineStr">
+      <c r="A11" s="108" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="B11" s="109" t="inlineStr">
+      <c r="B11" s="108" t="inlineStr">
         <is>
           <t>Number of people served or energy saved from transport and e-mobility interventions, such as electric vehicles or charging stations.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="43.5" customHeight="1">
-      <c r="A12" s="109" t="inlineStr">
+      <c r="A12" s="108" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
         </is>
       </c>
-      <c r="B12" s="109" t="inlineStr">
+      <c r="B12" s="108" t="inlineStr">
         <is>
           <t>Energy saved from energy-efficiency interventions, such as building or industrial efficiency.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="29.1" customHeight="1">
-      <c r="A13" s="109" t="inlineStr">
+      <c r="A13" s="108" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
         </is>
       </c>
-      <c r="B13" s="109" t="inlineStr">
+      <c r="B13" s="108" t="inlineStr">
         <is>
           <t>Number of people benefiting from energy infrastructure interventions, such as streetlights, transmission, and distribution lines.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="109" t="inlineStr">
+      <c r="A14" s="108" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
         </is>
       </c>
-      <c r="B14" s="109" t="inlineStr">
+      <c r="B14" s="108" t="inlineStr">
         <is>
           <t>Access to other energy services not captured by the categories above.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="29.1" customHeight="1">
-      <c r="A15" s="109" t="inlineStr">
+      <c r="A15" s="108" t="inlineStr">
         <is>
           <t>Financing support</t>
         </is>
       </c>
-      <c r="B15" s="109" t="inlineStr">
+      <c r="B15" s="108" t="inlineStr">
         <is>
           <t>Support for the development of the energy market ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="29.1" customHeight="1">
-      <c r="A16" s="109" t="inlineStr">
+      <c r="A16" s="108" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
         </is>
       </c>
-      <c r="B16" s="109" t="inlineStr">
+      <c r="B16" s="108" t="inlineStr">
         <is>
           <t>Support for the development of medium enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="29.1" customHeight="1">
-      <c r="A17" s="109" t="inlineStr">
+      <c r="A17" s="108" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
         </is>
       </c>
-      <c r="B17" s="109" t="inlineStr">
+      <c r="B17" s="108" t="inlineStr">
         <is>
           <t>Support for the development of small enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="29.1" customHeight="1">
-      <c r="A18" s="109" t="inlineStr">
+      <c r="A18" s="108" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="B18" s="109" t="inlineStr">
+      <c r="B18" s="108" t="inlineStr">
         <is>
           <t>Number of people benefiting from training on energy business, energy finance, or related implementation capacity.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="72.59999999999999" customHeight="1">
-      <c r="A19" s="109" t="inlineStr">
+      <c r="A19" s="108" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
         </is>
       </c>
-      <c r="B19" s="109" t="inlineStr">
+      <c r="B19" s="108" t="inlineStr">
         <is>
           <t>Training for enterprises on the energy business, assumed to result in direct beneficiaries.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="29.1" customHeight="1">
-      <c r="A20" s="109" t="inlineStr">
+      <c r="A20" s="108" t="inlineStr">
         <is>
           <t>Market Intervention</t>
         </is>
       </c>
-      <c r="B20" s="109" t="inlineStr">
+      <c r="B20" s="108" t="inlineStr">
         <is>
           <t>Volume of investment leveraged or barriers removed for clean, reliable, affordable, and sustainable energy solutions.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="43.5" customHeight="1">
-      <c r="A21" s="109" t="inlineStr">
+      <c r="A21" s="108" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
         </is>
       </c>
-      <c r="B21" s="109" t="inlineStr">
+      <c r="B21" s="108" t="inlineStr">
         <is>
           <t>Individuals who participate in advocacy or awareness campaigns on energy.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="29.1" customHeight="1">
-      <c r="A22" s="109" t="inlineStr">
+      <c r="A22" s="108" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="B22" s="109" t="inlineStr">
+      <c r="B22" s="108" t="inlineStr">
         <is>
           <t>Policies, regulations, strategies, plans, or frameworks developed, approved, implemented, or strengthened.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="109" t="inlineStr">
+      <c r="A23" s="108" t="inlineStr">
         <is>
           <t>GHG Emissions Reduction</t>
         </is>
       </c>
-      <c r="B23" s="109" t="inlineStr">
+      <c r="B23" s="108" t="inlineStr">
         <is>
           <t>Greenhouse gas emissions reduced or mitigated, in tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="109" t="inlineStr">
+      <c r="A24" s="108" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="109" t="inlineStr">
+      <c r="B24" s="108" t="inlineStr">
         <is>
           <t>Energy-related output that does not fit the standard categories above.</t>
         </is>
